--- a/ExportExcel/Update to Cart Test.xlsx
+++ b/ExportExcel/Update to Cart Test.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="18">
   <si>
     <t>STT</t>
   </si>
@@ -38,22 +38,34 @@
     <t/>
   </si>
   <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>2 ms</t>
-  </si>
-  <si>
-    <t>Cannot invoke "org.openqa.selenium.support.ui.WebDriverWait.until(java.util.function.Function)" because "this.wait" is null</t>
-  </si>
-  <si>
-    <t>0 ms</t>
-  </si>
-  <si>
-    <t>1 ms</t>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>13493 ms</t>
+  </si>
+  <si>
+    <t>13461 ms</t>
+  </si>
+  <si>
+    <t>13416 ms</t>
+  </si>
+  <si>
+    <t>13408 ms</t>
+  </si>
+  <si>
+    <t>13410 ms</t>
   </si>
   <si>
     <t>testUpdateCard</t>
+  </si>
+  <si>
+    <t>9694 ms</t>
+  </si>
+  <si>
+    <t>17838 ms</t>
+  </si>
+  <si>
+    <t>9649 ms</t>
   </si>
 </sst>
 </file>
@@ -126,9 +138,9 @@
     <col min="1" max="1" width="3.76171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="13.7265625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.52734375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="6.484375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="7.08203125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="13.2109375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="100.69140625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="18.703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -161,14 +173,14 @@
       <c r="C2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="2">
+      <c r="D2" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>9</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -181,14 +193,14 @@
       <c r="C3" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D3" t="s" s="2">
+      <c r="D3" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -201,14 +213,14 @@
       <c r="C4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D4" t="s" s="2">
+      <c r="D4" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E4" t="s" s="0">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -221,14 +233,14 @@
       <c r="C5" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D5" t="s" s="2">
+      <c r="D5" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -241,14 +253,14 @@
       <c r="C6" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D6" t="s" s="2">
+      <c r="D6" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -256,19 +268,19 @@
         <v>6.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D7" t="s" s="2">
+      <c r="D7" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -276,19 +288,19 @@
         <v>7.0</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D8" t="s" s="2">
+      <c r="D8" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -296,19 +308,19 @@
         <v>8.0</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D9" t="s" s="2">
+      <c r="D9" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
